--- a/OI/jeu_du_lean_manufacturing/Tableau de bord.xlsx
+++ b/OI/jeu_du_lean_manufacturing/Tableau de bord.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cfaicentre-my.sharepoint.com/personal/s_jaubert_poleformation-uimmcvdl_fr/Documents/00FC/OI/jeu_du_lean_manufacturing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{8B36CB23-4493-4B11-B332-DA89B4F93BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18EDDD14-B9E6-4B0D-B129-2F1E1CBA42D3}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{8B36CB23-4493-4B11-B332-DA89B4F93BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86CB44A1-4035-4F68-944F-2A610B75C923}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="713" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="17472" windowHeight="10992" tabRatio="713" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sommaire" sheetId="13" r:id="rId1"/>
@@ -18,22 +18,23 @@
     <sheet name="Qualité" sheetId="1" r:id="rId3"/>
     <sheet name="Performances Simul. 1" sheetId="27" r:id="rId4"/>
     <sheet name="Takt Time" sheetId="28" r:id="rId5"/>
-    <sheet name="TRG" sheetId="29" r:id="rId6"/>
-    <sheet name="Productivité" sheetId="30" r:id="rId7"/>
-    <sheet name="Graphique des flux" sheetId="20" r:id="rId8"/>
-    <sheet name="Enquête motivation" sheetId="21" r:id="rId9"/>
-    <sheet name="Performances Simul. 2" sheetId="31" r:id="rId10"/>
+    <sheet name="Feuil1" sheetId="32" r:id="rId6"/>
+    <sheet name="TRG" sheetId="29" r:id="rId7"/>
+    <sheet name="Productivité" sheetId="30" r:id="rId8"/>
+    <sheet name="Graphique des flux" sheetId="20" r:id="rId9"/>
+    <sheet name="Enquête motivation" sheetId="21" r:id="rId10"/>
+    <sheet name="Performances Simul. 2" sheetId="31" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="caseA" localSheetId="4">#REF!</definedName>
-    <definedName name="Diagnostic" localSheetId="7">#REF!</definedName>
+    <definedName name="Diagnostic" localSheetId="8">#REF!</definedName>
     <definedName name="Diagnostic" localSheetId="4">#REF!</definedName>
-    <definedName name="Importance" localSheetId="7">#REF!</definedName>
+    <definedName name="Importance" localSheetId="8">#REF!</definedName>
     <definedName name="Importance" localSheetId="4">#REF!</definedName>
     <definedName name="titre" localSheetId="4">#REF!</definedName>
     <definedName name="titre2" localSheetId="4">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -115,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="154">
   <si>
     <t>Croix</t>
   </si>
@@ -813,6 +814,30 @@
   </si>
   <si>
     <t>Résultats Atelier 3</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>TaktTime</t>
+  </si>
+  <si>
+    <t>Temps Cycle</t>
   </si>
 </sst>
 </file>
@@ -2361,10 +2386,76 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="166" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="22" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="22" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2402,69 +2493,6 @@
     <xf numFmtId="0" fontId="11" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="22" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="22" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="50" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -2498,11 +2526,45 @@
     <xf numFmtId="3" fontId="18" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="19" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="57" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="58" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="26" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2515,74 +2577,43 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="57" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="58" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="59" fillId="11" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="20" fillId="36" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="62" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="60" fillId="35" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="9" fontId="20" fillId="2" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="20" fillId="36" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="32" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2592,13 +2623,7 @@
     <xf numFmtId="0" fontId="60" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="36" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2916,25 +2941,25 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0.2</c:v>
+                  <c:v>0.12</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5</c:v>
+                  <c:v>4.6511627906976744E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.0909090909090912E-2</c:v>
+                  <c:v>0.10526315789473684</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22222222222222221</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.125</c:v>
+                  <c:v>0.14705882352941177</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0.125</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.20833333333333334</c:v>
+                  <c:v>0.20895522388059701</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3162,7 +3187,7 @@
                 <c:formatCode>0"s. (Rec.)"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>115</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3194,7 +3219,7 @@
                 <c:formatCode>0" s."</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>9.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3226,7 +3251,7 @@
                 <c:formatCode>0"s. (Eto.)"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>180</c:v>
+                  <c:v>230.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3258,7 +3283,7 @@
                 <c:formatCode>0" s."</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>16.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3290,7 +3315,7 @@
                 <c:formatCode>0"s. (Vag.)"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>120</c:v>
+                  <c:v>103.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3322,7 +3347,7 @@
                 <c:formatCode>0" s."</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>11.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3354,7 +3379,7 @@
                 <c:formatCode>0"s. (Tri.)"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>240</c:v>
+                  <c:v>48.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3386,7 +3411,7 @@
                 <c:formatCode>0" s."</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3418,7 +3443,7 @@
                 <c:formatCode>0"s. (Co.)"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>240</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3655,7 +3680,7 @@
                 <c:formatCode>0"s. (Rec.)"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>115</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3685,7 +3710,7 @@
                 <c:formatCode>0" s."</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>9.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3754,7 +3779,7 @@
                 <c:formatCode>0"s. (Eto.)"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>180</c:v>
+                  <c:v>230.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3784,7 +3809,7 @@
                 <c:formatCode>0" s."</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>16.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3853,7 +3878,7 @@
                 <c:formatCode>0"s. (Vag.)"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>120</c:v>
+                  <c:v>103.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3883,7 +3908,7 @@
                 <c:formatCode>0" s."</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>11.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3952,7 +3977,7 @@
                 <c:formatCode>0"s. (Tri.)"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>240</c:v>
+                  <c:v>48.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3982,7 +4007,7 @@
                 <c:formatCode>0" s."</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4051,7 +4076,7 @@
                 <c:formatCode>0"s. (Co.)"</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>240</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4387,7 +4412,7 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.736842105263158</c:v>
+                  <c:v>12.037735849056604</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>10</c:v>
@@ -4755,7 +4780,7 @@
                   <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>135</c:v>
+                  <c:v>105</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>60</c:v>
@@ -5490,7 +5515,7 @@
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.8</c:v>
+                  <c:v>17.600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>8</c:v>
@@ -5774,7 +5799,7 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.736842105263158</c:v>
+                  <c:v>12.037735849056604</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6047,7 +6072,7 @@
                   <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>135</c:v>
+                  <c:v>105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6593,7 +6618,7 @@
                   <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20.8</c:v>
+                  <c:v>17.600000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7245,22 +7270,22 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.22916666666666666</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.46979166666666666</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.43680555555555556</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.35208333333333336</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.60416666666666663</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.22847222222222222</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8155,8 +8180,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7005867" y="4113353"/>
-          <a:ext cx="3949764" cy="296987"/>
+          <a:off x="7536373" y="4113353"/>
+          <a:ext cx="4263245" cy="301810"/>
           <a:chOff x="8190939" y="2049556"/>
           <a:chExt cx="4784679" cy="398786"/>
         </a:xfrm>
@@ -8590,8 +8615,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1106733" y="1278038"/>
-          <a:ext cx="4588301" cy="501473"/>
+          <a:off x="1188720" y="1278038"/>
+          <a:ext cx="4896959" cy="501473"/>
           <a:chOff x="7438380" y="4356708"/>
           <a:chExt cx="4616473" cy="413212"/>
         </a:xfrm>
@@ -9145,8 +9170,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1249680" y="351834"/>
-          <a:ext cx="2760542" cy="281940"/>
+          <a:off x="1346901" y="347892"/>
+          <a:ext cx="2977318" cy="281940"/>
           <a:chOff x="3087147" y="2409825"/>
           <a:chExt cx="2959861" cy="301073"/>
         </a:xfrm>
@@ -9537,8 +9562,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="990862" y="1486689"/>
-          <a:ext cx="3035650" cy="290611"/>
+          <a:off x="1002686" y="1473551"/>
+          <a:ext cx="3337823" cy="274845"/>
           <a:chOff x="3087147" y="2409825"/>
           <a:chExt cx="2959861" cy="301073"/>
         </a:xfrm>
@@ -10277,8 +10302,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1453515" y="817245"/>
-          <a:ext cx="3381375" cy="266700"/>
+          <a:off x="1565910" y="815340"/>
+          <a:ext cx="3638550" cy="266700"/>
           <a:chOff x="3087147" y="2409825"/>
           <a:chExt cx="2959861" cy="301073"/>
         </a:xfrm>
@@ -10730,8 +10755,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1703236" y="784529"/>
-          <a:ext cx="2652505" cy="270013"/>
+          <a:off x="1835757" y="784529"/>
+          <a:ext cx="2911669" cy="266700"/>
           <a:chOff x="3087147" y="2409825"/>
           <a:chExt cx="2959861" cy="301073"/>
         </a:xfrm>
@@ -11122,8 +11147,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5303189" y="837869"/>
-          <a:ext cx="3485984" cy="395246"/>
+          <a:off x="5733884" y="837869"/>
+          <a:ext cx="3770906" cy="388620"/>
           <a:chOff x="3087147" y="2409825"/>
           <a:chExt cx="2959861" cy="301073"/>
         </a:xfrm>
@@ -13189,6 +13214,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
@@ -13480,40 +13509,40 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:E29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.41796875" defaultRowHeight="13.8" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="2.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="39.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="39.28515625" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="2.26171875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.41796875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="39.26171875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="6.41796875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="39.26171875" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="11.41796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="144" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="135"/>
       <c r="C2" s="130" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="135"/>
       <c r="B3" s="135"/>
       <c r="C3" s="130" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="4.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="129"/>
       <c r="B4" s="129"/>
     </row>
-    <row r="5" spans="1:5" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="214" t="s">
+    <row r="5" spans="1:5" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="215" t="s">
         <v>114</v>
       </c>
       <c r="C5" s="136" t="s">
@@ -13524,14 +13553,14 @@
       </c>
       <c r="E5"/>
     </row>
-    <row r="6" spans="1:5" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="215"/>
+    <row r="6" spans="1:5" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="216"/>
       <c r="C6" s="3"/>
       <c r="D6" s="145"/>
       <c r="E6" s="3"/>
     </row>
-    <row r="7" spans="1:5" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="215"/>
+    <row r="7" spans="1:5" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="216"/>
       <c r="C7" s="137" t="s">
         <v>44</v>
       </c>
@@ -13540,14 +13569,14 @@
       </c>
       <c r="E7" s="3"/>
     </row>
-    <row r="8" spans="1:5" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="215"/>
+    <row r="8" spans="1:5" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="216"/>
       <c r="C8" s="3"/>
       <c r="D8" s="145"/>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" spans="1:5" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="215"/>
+    <row r="9" spans="1:5" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="216"/>
       <c r="C9" s="138" t="s">
         <v>117</v>
       </c>
@@ -13556,14 +13585,14 @@
       </c>
       <c r="E9"/>
     </row>
-    <row r="10" spans="1:5" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="215"/>
+    <row r="10" spans="1:5" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="216"/>
       <c r="C10" s="3"/>
       <c r="D10" s="145"/>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="1:5" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="215"/>
+    <row r="11" spans="1:5" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="216"/>
       <c r="C11" s="139" t="s">
         <v>83</v>
       </c>
@@ -13572,14 +13601,14 @@
       </c>
       <c r="E11" s="130"/>
     </row>
-    <row r="12" spans="1:5" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="215"/>
+    <row r="12" spans="1:5" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="216"/>
       <c r="C12" s="3"/>
       <c r="D12" s="145"/>
       <c r="E12" s="130"/>
     </row>
-    <row r="13" spans="1:5" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="216"/>
+    <row r="13" spans="1:5" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="217"/>
       <c r="C13" s="140" t="s">
         <v>131</v>
       </c>
@@ -13588,16 +13617,16 @@
       </c>
       <c r="E13" s="130"/>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="D14" s="130"/>
       <c r="E14" s="130"/>
     </row>
-    <row r="15" spans="1:5" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="D15" s="130"/>
       <c r="E15" s="130"/>
     </row>
-    <row r="16" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="213" t="s">
+    <row r="16" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="214" t="s">
         <v>111</v>
       </c>
       <c r="C16" s="133" t="s">
@@ -13608,13 +13637,13 @@
       </c>
       <c r="E16" s="130"/>
     </row>
-    <row r="17" spans="2:5" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="213"/>
+    <row r="17" spans="2:5" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="214"/>
       <c r="D17" s="145"/>
       <c r="E17" s="130"/>
     </row>
-    <row r="18" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="213"/>
+    <row r="18" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="214"/>
       <c r="C18" s="132" t="s">
         <v>126</v>
       </c>
@@ -13623,13 +13652,13 @@
       </c>
       <c r="E18" s="130"/>
     </row>
-    <row r="19" spans="2:5" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="213"/>
+    <row r="19" spans="2:5" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="214"/>
       <c r="D19" s="146"/>
       <c r="E19" s="130"/>
     </row>
-    <row r="20" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="213"/>
+    <row r="20" spans="2:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="214"/>
       <c r="C20" s="134" t="s">
         <v>104</v>
       </c>
@@ -13638,7 +13667,7 @@
       </c>
       <c r="E20" s="130"/>
     </row>
-    <row r="22" spans="2:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" ht="15" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="143" t="s">
         <v>62</v>
       </c>
@@ -13649,7 +13678,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="24" spans="2:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" ht="14.1" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="131" t="s">
         <v>13</v>
       </c>
@@ -13657,15 +13686,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.55000000000000004">
       <c r="C25" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="2:5" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" ht="6.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="2:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" ht="14.1" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="131" t="s">
         <v>16</v>
       </c>
@@ -13673,8 +13702,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="2:5" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="2:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" ht="9" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="29" spans="2:5" ht="14.1" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="131" t="s">
         <v>112</v>
       </c>
@@ -13705,86 +13734,304 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.41796875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="4.26171875" customWidth="1"/>
+    <col min="2" max="2" width="4.41796875" customWidth="1"/>
+    <col min="3" max="3" width="104.26171875" customWidth="1"/>
+    <col min="4" max="7" width="5.68359375" style="98" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="17.7" x14ac:dyDescent="0.6">
+      <c r="A1" s="242" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="242"/>
+      <c r="C1" s="242"/>
+      <c r="D1" s="242"/>
+      <c r="E1" s="242"/>
+      <c r="F1" s="242"/>
+      <c r="G1" s="242"/>
+    </row>
+    <row r="2" spans="1:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="3" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D3" s="108" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="108" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="108" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="99"/>
+      <c r="C4" s="100" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="101" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="101" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="102" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="103">
+        <v>1</v>
+      </c>
+      <c r="C5" s="104" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="95"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="97"/>
+    </row>
+    <row r="6" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="103">
+        <v>2</v>
+      </c>
+      <c r="C6" s="104" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="95"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="96"/>
+      <c r="G6" s="97"/>
+    </row>
+    <row r="7" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="103">
+        <v>3</v>
+      </c>
+      <c r="C7" s="104" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="95"/>
+      <c r="E7" s="96"/>
+      <c r="F7" s="96"/>
+      <c r="G7" s="97"/>
+    </row>
+    <row r="8" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="103">
+        <v>4</v>
+      </c>
+      <c r="C8" s="104" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="95"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="97"/>
+    </row>
+    <row r="9" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="103">
+        <v>5</v>
+      </c>
+      <c r="C9" s="104" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="95"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="97"/>
+    </row>
+    <row r="10" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="103">
+        <v>6</v>
+      </c>
+      <c r="C10" s="104" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="95"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="97"/>
+    </row>
+    <row r="11" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="103">
+        <v>7</v>
+      </c>
+      <c r="C11" s="104" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="95"/>
+      <c r="E11" s="96"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="97"/>
+    </row>
+    <row r="12" spans="1:7" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B12" s="105">
+        <v>8</v>
+      </c>
+      <c r="C12" s="106" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="95"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="96"/>
+      <c r="G12" s="97"/>
+    </row>
+    <row r="13" spans="1:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="14" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D14" s="107">
+        <f>SUM(D5:D12)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="107">
+        <f>SUM(E5:E12)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="107">
+        <f>SUM(F5:F12)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="107">
+        <f>SUM(G5:G12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="16" spans="1:7" ht="20.100000000000001" x14ac:dyDescent="0.7">
+      <c r="D16" s="109" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="241">
+        <f>SUM(D14:G14)/32</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="241"/>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="2">
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D5:D12">
+    <cfRule type="cellIs" dxfId="3" priority="8" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:E12">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
+      <formula>2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F12">
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+      <formula>3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G12">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="A1:G1" location="Sommaire!A1" display="Enquête Motivation" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:W48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.41796875" defaultRowHeight="13.8" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.41796875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
-    <col min="3" max="4" width="9.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="7.42578125" style="2" customWidth="1"/>
+    <col min="3" max="4" width="9.41796875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.41796875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="7.41796875" style="2" customWidth="1"/>
     <col min="7" max="7" width="6" style="2" customWidth="1"/>
-    <col min="8" max="8" width="5.42578125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.42578125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="2"/>
+    <col min="8" max="8" width="5.41796875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="4.68359375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.41796875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9.68359375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="9.15625" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="11.41796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="195" t="s">
+    <row r="1" spans="1:23" ht="17.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="183" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="195"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
-      <c r="H1" s="195"/>
-      <c r="I1" s="195"/>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
-      <c r="V1" s="195"/>
-      <c r="W1" s="195"/>
-    </row>
-    <row r="2" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="218" t="s">
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
+      <c r="J1" s="183"/>
+      <c r="K1" s="183"/>
+      <c r="L1" s="183"/>
+      <c r="M1" s="183"/>
+      <c r="N1" s="183"/>
+      <c r="O1" s="183"/>
+      <c r="P1" s="183"/>
+      <c r="Q1" s="183"/>
+      <c r="R1" s="183"/>
+      <c r="S1" s="183"/>
+      <c r="T1" s="183"/>
+      <c r="U1" s="183"/>
+      <c r="V1" s="183"/>
+      <c r="W1" s="183"/>
+    </row>
+    <row r="2" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="3" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C3" s="219" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="218"/>
-      <c r="E3" s="218"/>
-      <c r="F3" s="218"/>
-      <c r="G3" s="218"/>
-      <c r="H3" s="218"/>
-      <c r="I3" s="218"/>
-      <c r="J3" s="218"/>
-    </row>
-    <row r="4" spans="1:23" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="220" t="s">
+      <c r="D3" s="219"/>
+      <c r="E3" s="219"/>
+      <c r="F3" s="219"/>
+      <c r="G3" s="219"/>
+      <c r="H3" s="219"/>
+      <c r="I3" s="219"/>
+      <c r="J3" s="219"/>
+    </row>
+    <row r="4" spans="1:23" ht="33.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C4" s="221" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="221"/>
-      <c r="E4" s="219" t="s">
+      <c r="D4" s="222"/>
+      <c r="E4" s="220" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="219"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="220"/>
+      <c r="G4" s="220" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="219"/>
-      <c r="I4" s="219" t="s">
+      <c r="H4" s="220"/>
+      <c r="I4" s="220" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="219"/>
-    </row>
-    <row r="5" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J4" s="220"/>
+    </row>
+    <row r="5" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="35" t="s">
         <v>42</v>
       </c>
@@ -13817,7 +14064,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="41" t="s">
         <v>70</v>
       </c>
@@ -13850,29 +14097,29 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="47" t="s">
         <v>76</v>
       </c>
       <c r="C7" s="47">
         <f>'Données Simulation 1'!H20</f>
-        <v>4.7368421052631584</v>
+        <v>2.0377358490566038</v>
       </c>
       <c r="D7" s="48">
         <f>10+C7</f>
-        <v>14.736842105263158</v>
+        <v>12.037735849056604</v>
       </c>
       <c r="E7" s="47">
         <f>('Données Simulation 1'!P11*60+'Données Simulation 1'!Q11)/60</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F7" s="49">
         <f>60+5*E7</f>
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="G7" s="50">
         <f>'Données Simulation 1'!J13</f>
-        <v>0.20833333333333334</v>
+        <v>0.20895522388059701</v>
       </c>
       <c r="H7" s="51">
         <f>MAX(100-G7*100*5,0)</f>
@@ -13880,14 +14127,14 @@
       </c>
       <c r="I7" s="51">
         <f>'Données Simulation 1'!S15</f>
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J7" s="52">
         <f>8+I7*2/5</f>
-        <v>20.8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="53" t="s">
         <v>75</v>
       </c>
@@ -13912,19 +14159,19 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="242" t="s">
+    <row r="9" spans="1:23" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C9" s="255" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="242"/>
-      <c r="E9" s="242"/>
-      <c r="F9" s="242"/>
-      <c r="G9" s="242"/>
-      <c r="H9" s="242"/>
-      <c r="I9" s="242"/>
-      <c r="J9" s="242"/>
-    </row>
-    <row r="10" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D9" s="255"/>
+      <c r="E9" s="255"/>
+      <c r="F9" s="255"/>
+      <c r="G9" s="255"/>
+      <c r="H9" s="255"/>
+      <c r="I9" s="255"/>
+      <c r="J9" s="255"/>
+    </row>
+    <row r="10" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="58" t="s">
         <v>71</v>
       </c>
@@ -13949,7 +14196,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="63" t="s">
         <v>72</v>
       </c>
@@ -13974,7 +14221,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="68" t="s">
         <v>73</v>
       </c>
@@ -13999,440 +14246,432 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="250" t="s">
+    <row r="18" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="252" t="s">
         <v>143</v>
       </c>
-      <c r="C18" s="250"/>
-      <c r="D18" s="250"/>
-      <c r="E18" s="250"/>
-      <c r="F18" s="250"/>
-      <c r="G18" s="250"/>
-      <c r="H18" s="250"/>
-      <c r="I18" s="250"/>
-      <c r="J18" s="250"/>
-    </row>
-    <row r="19" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="251" t="s">
+      <c r="C18" s="252"/>
+      <c r="D18" s="252"/>
+      <c r="E18" s="252"/>
+      <c r="F18" s="252"/>
+      <c r="G18" s="252"/>
+      <c r="H18" s="252"/>
+      <c r="I18" s="252"/>
+      <c r="J18" s="252"/>
+    </row>
+    <row r="19" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" s="253" t="s">
         <v>134</v>
       </c>
-      <c r="C19" s="251"/>
-      <c r="D19" s="251"/>
-      <c r="E19" s="251"/>
-      <c r="F19" s="251"/>
+      <c r="C19" s="253"/>
+      <c r="D19" s="253"/>
+      <c r="E19" s="253"/>
+      <c r="F19" s="253"/>
       <c r="G19" s="176"/>
-      <c r="H19" s="252" t="s">
+      <c r="H19" s="254" t="s">
         <v>141</v>
       </c>
-      <c r="I19" s="252"/>
-      <c r="J19" s="252"/>
-    </row>
-    <row r="20" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="244" t="s">
+      <c r="I19" s="254"/>
+      <c r="J19" s="254"/>
+    </row>
+    <row r="20" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="249" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="244"/>
-      <c r="D20" s="244"/>
-      <c r="E20" s="245">
+      <c r="C20" s="249"/>
+      <c r="D20" s="249"/>
+      <c r="E20" s="248">
         <v>24</v>
       </c>
-      <c r="F20" s="245"/>
+      <c r="F20" s="248"/>
       <c r="G20" s="176"/>
-      <c r="H20" s="245"/>
-      <c r="I20" s="245"/>
-      <c r="J20" s="245"/>
-    </row>
-    <row r="21" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="244" t="s">
+      <c r="H20" s="248"/>
+      <c r="I20" s="248"/>
+      <c r="J20" s="248"/>
+    </row>
+    <row r="21" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="C21" s="244"/>
-      <c r="D21" s="244"/>
-      <c r="E21" s="245"/>
-      <c r="F21" s="245"/>
+      <c r="C21" s="249"/>
+      <c r="D21" s="249"/>
+      <c r="E21" s="248"/>
+      <c r="F21" s="248"/>
       <c r="G21" s="176"/>
-      <c r="H21" s="246" t="s">
+      <c r="H21" s="250" t="s">
         <v>142</v>
       </c>
-      <c r="I21" s="246"/>
-      <c r="J21" s="246"/>
-    </row>
-    <row r="22" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="244" t="s">
+      <c r="I21" s="250"/>
+      <c r="J21" s="250"/>
+    </row>
+    <row r="22" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="249" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="244"/>
-      <c r="D22" s="244"/>
-      <c r="E22" s="247">
+      <c r="C22" s="249"/>
+      <c r="D22" s="249"/>
+      <c r="E22" s="251">
         <f>(24-E21)/24</f>
         <v>1</v>
       </c>
-      <c r="F22" s="247"/>
+      <c r="F22" s="251"/>
       <c r="G22" s="176"/>
-      <c r="H22" s="245"/>
-      <c r="I22" s="245"/>
-      <c r="J22" s="245"/>
-    </row>
-    <row r="23" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="248" t="s">
+      <c r="H22" s="248"/>
+      <c r="I22" s="248"/>
+      <c r="J22" s="248"/>
+    </row>
+    <row r="23" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23" s="246" t="s">
         <v>135</v>
       </c>
-      <c r="C23" s="248"/>
-      <c r="D23" s="248"/>
-      <c r="E23" s="248"/>
-      <c r="F23" s="248"/>
+      <c r="C23" s="246"/>
+      <c r="D23" s="246"/>
+      <c r="E23" s="246"/>
+      <c r="F23" s="246"/>
       <c r="G23" s="176"/>
       <c r="H23" s="176"/>
-      <c r="I23" s="243"/>
-      <c r="J23" s="243"/>
-    </row>
-    <row r="24" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="254" t="s">
+      <c r="I23" s="247"/>
+      <c r="J23" s="247"/>
+    </row>
+    <row r="24" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24" s="243" t="s">
         <v>138</v>
       </c>
-      <c r="C24" s="254"/>
-      <c r="D24" s="254"/>
-      <c r="E24" s="245"/>
-      <c r="F24" s="245"/>
+      <c r="C24" s="243"/>
+      <c r="D24" s="243"/>
+      <c r="E24" s="248"/>
+      <c r="F24" s="248"/>
       <c r="G24" s="176"/>
       <c r="H24" s="176"/>
       <c r="I24" s="177"/>
       <c r="J24" s="177"/>
     </row>
-    <row r="25" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="254" t="s">
+    <row r="25" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25" s="243" t="s">
         <v>140</v>
       </c>
-      <c r="C25" s="254"/>
-      <c r="D25" s="254"/>
-      <c r="E25" s="245"/>
-      <c r="F25" s="245"/>
+      <c r="C25" s="243"/>
+      <c r="D25" s="243"/>
+      <c r="E25" s="248"/>
+      <c r="F25" s="248"/>
       <c r="G25" s="176"/>
       <c r="H25" s="176"/>
       <c r="I25" s="178"/>
       <c r="J25" s="178"/>
     </row>
-    <row r="26" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="254" t="s">
+    <row r="26" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26" s="243" t="s">
         <v>139</v>
       </c>
-      <c r="C26" s="254"/>
-      <c r="D26" s="254"/>
-      <c r="E26" s="249" t="str">
+      <c r="C26" s="243"/>
+      <c r="D26" s="243"/>
+      <c r="E26" s="244" t="str">
         <f>IF(E24=0,"",E24*E25/E21)</f>
         <v/>
       </c>
-      <c r="F26" s="249"/>
+      <c r="F26" s="244"/>
       <c r="G26" s="176"/>
       <c r="H26" s="176"/>
-      <c r="I26" s="253"/>
-      <c r="J26" s="253"/>
-    </row>
-    <row r="27" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="I26" s="245"/>
+      <c r="J26" s="245"/>
+    </row>
+    <row r="27" spans="2:10" ht="15" x14ac:dyDescent="0.55000000000000004">
       <c r="G27" s="176"/>
     </row>
-    <row r="29" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="250" t="s">
+    <row r="29" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29" s="252" t="s">
         <v>144</v>
       </c>
-      <c r="C29" s="250"/>
-      <c r="D29" s="250"/>
-      <c r="E29" s="250"/>
-      <c r="F29" s="250"/>
-      <c r="G29" s="250"/>
-      <c r="H29" s="250"/>
-      <c r="I29" s="250"/>
-      <c r="J29" s="250"/>
-    </row>
-    <row r="30" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="251" t="s">
+      <c r="C29" s="252"/>
+      <c r="D29" s="252"/>
+      <c r="E29" s="252"/>
+      <c r="F29" s="252"/>
+      <c r="G29" s="252"/>
+      <c r="H29" s="252"/>
+      <c r="I29" s="252"/>
+      <c r="J29" s="252"/>
+    </row>
+    <row r="30" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30" s="253" t="s">
         <v>134</v>
       </c>
-      <c r="C30" s="251"/>
-      <c r="D30" s="251"/>
-      <c r="E30" s="251"/>
-      <c r="F30" s="251"/>
+      <c r="C30" s="253"/>
+      <c r="D30" s="253"/>
+      <c r="E30" s="253"/>
+      <c r="F30" s="253"/>
       <c r="G30" s="176"/>
-      <c r="H30" s="252" t="s">
+      <c r="H30" s="254" t="s">
         <v>141</v>
       </c>
-      <c r="I30" s="252"/>
-      <c r="J30" s="252"/>
-    </row>
-    <row r="31" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="244" t="s">
+      <c r="I30" s="254"/>
+      <c r="J30" s="254"/>
+    </row>
+    <row r="31" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31" s="249" t="s">
         <v>136</v>
       </c>
-      <c r="C31" s="244"/>
-      <c r="D31" s="244"/>
-      <c r="E31" s="245">
+      <c r="C31" s="249"/>
+      <c r="D31" s="249"/>
+      <c r="E31" s="248">
         <v>24</v>
       </c>
-      <c r="F31" s="245"/>
+      <c r="F31" s="248"/>
       <c r="G31" s="176"/>
-      <c r="H31" s="245"/>
-      <c r="I31" s="245"/>
-      <c r="J31" s="245"/>
-    </row>
-    <row r="32" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="244" t="s">
+      <c r="H31" s="248"/>
+      <c r="I31" s="248"/>
+      <c r="J31" s="248"/>
+    </row>
+    <row r="32" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="C32" s="244"/>
-      <c r="D32" s="244"/>
-      <c r="E32" s="245"/>
-      <c r="F32" s="245"/>
+      <c r="C32" s="249"/>
+      <c r="D32" s="249"/>
+      <c r="E32" s="248"/>
+      <c r="F32" s="248"/>
       <c r="G32" s="176"/>
-      <c r="H32" s="246" t="s">
+      <c r="H32" s="250" t="s">
         <v>142</v>
       </c>
-      <c r="I32" s="246"/>
-      <c r="J32" s="246"/>
-    </row>
-    <row r="33" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="244" t="s">
+      <c r="I32" s="250"/>
+      <c r="J32" s="250"/>
+    </row>
+    <row r="33" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33" s="249" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="244"/>
-      <c r="D33" s="244"/>
-      <c r="E33" s="247">
+      <c r="C33" s="249"/>
+      <c r="D33" s="249"/>
+      <c r="E33" s="251">
         <f>(24-E32)/24</f>
         <v>1</v>
       </c>
-      <c r="F33" s="247"/>
+      <c r="F33" s="251"/>
       <c r="G33" s="176"/>
-      <c r="H33" s="245"/>
-      <c r="I33" s="245"/>
-      <c r="J33" s="245"/>
-    </row>
-    <row r="34" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="248" t="s">
+      <c r="H33" s="248"/>
+      <c r="I33" s="248"/>
+      <c r="J33" s="248"/>
+    </row>
+    <row r="34" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B34" s="246" t="s">
         <v>135</v>
       </c>
-      <c r="C34" s="248"/>
-      <c r="D34" s="248"/>
-      <c r="E34" s="248"/>
-      <c r="F34" s="248"/>
+      <c r="C34" s="246"/>
+      <c r="D34" s="246"/>
+      <c r="E34" s="246"/>
+      <c r="F34" s="246"/>
       <c r="G34" s="176"/>
       <c r="H34" s="176"/>
-      <c r="I34" s="243"/>
-      <c r="J34" s="243"/>
-    </row>
-    <row r="35" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="254" t="s">
+      <c r="I34" s="247"/>
+      <c r="J34" s="247"/>
+    </row>
+    <row r="35" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="243" t="s">
         <v>138</v>
       </c>
-      <c r="C35" s="254"/>
-      <c r="D35" s="254"/>
-      <c r="E35" s="245"/>
-      <c r="F35" s="245"/>
+      <c r="C35" s="243"/>
+      <c r="D35" s="243"/>
+      <c r="E35" s="248"/>
+      <c r="F35" s="248"/>
       <c r="G35" s="176"/>
       <c r="H35" s="176"/>
       <c r="I35" s="177"/>
       <c r="J35" s="177"/>
     </row>
-    <row r="36" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="254" t="s">
+    <row r="36" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36" s="243" t="s">
         <v>140</v>
       </c>
-      <c r="C36" s="254"/>
-      <c r="D36" s="254"/>
-      <c r="E36" s="245"/>
-      <c r="F36" s="245"/>
+      <c r="C36" s="243"/>
+      <c r="D36" s="243"/>
+      <c r="E36" s="248"/>
+      <c r="F36" s="248"/>
       <c r="G36" s="176"/>
       <c r="H36" s="176"/>
       <c r="I36" s="178"/>
       <c r="J36" s="178"/>
     </row>
-    <row r="37" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="254" t="s">
+    <row r="37" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="243" t="s">
         <v>139</v>
       </c>
-      <c r="C37" s="254"/>
-      <c r="D37" s="254"/>
-      <c r="E37" s="249" t="str">
+      <c r="C37" s="243"/>
+      <c r="D37" s="243"/>
+      <c r="E37" s="244" t="str">
         <f>IF(E35=0,"",E35*E36/E32)</f>
         <v/>
       </c>
-      <c r="F37" s="249"/>
+      <c r="F37" s="244"/>
       <c r="G37" s="176"/>
       <c r="H37" s="176"/>
-      <c r="I37" s="253"/>
-      <c r="J37" s="253"/>
-    </row>
-    <row r="40" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="250" t="s">
+      <c r="I37" s="245"/>
+      <c r="J37" s="245"/>
+    </row>
+    <row r="40" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="252" t="s">
         <v>145</v>
       </c>
-      <c r="C40" s="250"/>
-      <c r="D40" s="250"/>
-      <c r="E40" s="250"/>
-      <c r="F40" s="250"/>
-      <c r="G40" s="250"/>
-      <c r="H40" s="250"/>
-      <c r="I40" s="250"/>
-      <c r="J40" s="250"/>
-    </row>
-    <row r="41" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="251" t="s">
+      <c r="C40" s="252"/>
+      <c r="D40" s="252"/>
+      <c r="E40" s="252"/>
+      <c r="F40" s="252"/>
+      <c r="G40" s="252"/>
+      <c r="H40" s="252"/>
+      <c r="I40" s="252"/>
+      <c r="J40" s="252"/>
+    </row>
+    <row r="41" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="253" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="251"/>
-      <c r="D41" s="251"/>
-      <c r="E41" s="251"/>
-      <c r="F41" s="251"/>
+      <c r="C41" s="253"/>
+      <c r="D41" s="253"/>
+      <c r="E41" s="253"/>
+      <c r="F41" s="253"/>
       <c r="G41" s="176"/>
-      <c r="H41" s="252" t="s">
+      <c r="H41" s="254" t="s">
         <v>141</v>
       </c>
-      <c r="I41" s="252"/>
-      <c r="J41" s="252"/>
-    </row>
-    <row r="42" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="244" t="s">
+      <c r="I41" s="254"/>
+      <c r="J41" s="254"/>
+    </row>
+    <row r="42" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="249" t="s">
         <v>136</v>
       </c>
-      <c r="C42" s="244"/>
-      <c r="D42" s="244"/>
-      <c r="E42" s="245">
+      <c r="C42" s="249"/>
+      <c r="D42" s="249"/>
+      <c r="E42" s="248">
         <v>24</v>
       </c>
-      <c r="F42" s="245"/>
+      <c r="F42" s="248"/>
       <c r="G42" s="176"/>
-      <c r="H42" s="245"/>
-      <c r="I42" s="245"/>
-      <c r="J42" s="245"/>
-    </row>
-    <row r="43" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="244" t="s">
+      <c r="H42" s="248"/>
+      <c r="I42" s="248"/>
+      <c r="J42" s="248"/>
+    </row>
+    <row r="43" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="249" t="s">
         <v>137</v>
       </c>
-      <c r="C43" s="244"/>
-      <c r="D43" s="244"/>
-      <c r="E43" s="245"/>
-      <c r="F43" s="245"/>
+      <c r="C43" s="249"/>
+      <c r="D43" s="249"/>
+      <c r="E43" s="248"/>
+      <c r="F43" s="248"/>
       <c r="G43" s="176"/>
-      <c r="H43" s="246" t="s">
+      <c r="H43" s="250" t="s">
         <v>142</v>
       </c>
-      <c r="I43" s="246"/>
-      <c r="J43" s="246"/>
-    </row>
-    <row r="44" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="244" t="s">
+      <c r="I43" s="250"/>
+      <c r="J43" s="250"/>
+    </row>
+    <row r="44" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="249" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="244"/>
-      <c r="D44" s="244"/>
-      <c r="E44" s="247">
+      <c r="C44" s="249"/>
+      <c r="D44" s="249"/>
+      <c r="E44" s="251">
         <f>(24-E43)/24</f>
         <v>1</v>
       </c>
-      <c r="F44" s="247"/>
+      <c r="F44" s="251"/>
       <c r="G44" s="176"/>
-      <c r="H44" s="245"/>
-      <c r="I44" s="245"/>
-      <c r="J44" s="245"/>
-    </row>
-    <row r="45" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="248" t="s">
+      <c r="H44" s="248"/>
+      <c r="I44" s="248"/>
+      <c r="J44" s="248"/>
+    </row>
+    <row r="45" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="246" t="s">
         <v>135</v>
       </c>
-      <c r="C45" s="248"/>
-      <c r="D45" s="248"/>
-      <c r="E45" s="248"/>
-      <c r="F45" s="248"/>
+      <c r="C45" s="246"/>
+      <c r="D45" s="246"/>
+      <c r="E45" s="246"/>
+      <c r="F45" s="246"/>
       <c r="G45" s="176"/>
       <c r="H45" s="176"/>
-      <c r="I45" s="243"/>
-      <c r="J45" s="243"/>
-    </row>
-    <row r="46" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="254" t="s">
+      <c r="I45" s="247"/>
+      <c r="J45" s="247"/>
+    </row>
+    <row r="46" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="243" t="s">
         <v>138</v>
       </c>
-      <c r="C46" s="254"/>
-      <c r="D46" s="254"/>
-      <c r="E46" s="245"/>
-      <c r="F46" s="245"/>
+      <c r="C46" s="243"/>
+      <c r="D46" s="243"/>
+      <c r="E46" s="248"/>
+      <c r="F46" s="248"/>
       <c r="G46" s="176"/>
       <c r="H46" s="176"/>
       <c r="I46" s="177"/>
       <c r="J46" s="177"/>
     </row>
-    <row r="47" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="254" t="s">
+    <row r="47" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="243" t="s">
         <v>140</v>
       </c>
-      <c r="C47" s="254"/>
-      <c r="D47" s="254"/>
-      <c r="E47" s="245"/>
-      <c r="F47" s="245"/>
+      <c r="C47" s="243"/>
+      <c r="D47" s="243"/>
+      <c r="E47" s="248"/>
+      <c r="F47" s="248"/>
       <c r="G47" s="176"/>
       <c r="H47" s="176"/>
       <c r="I47" s="178"/>
       <c r="J47" s="178"/>
     </row>
-    <row r="48" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="254" t="s">
+    <row r="48" spans="2:10" ht="33.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="243" t="s">
         <v>139</v>
       </c>
-      <c r="C48" s="254"/>
-      <c r="D48" s="254"/>
-      <c r="E48" s="249" t="str">
+      <c r="C48" s="243"/>
+      <c r="D48" s="243"/>
+      <c r="E48" s="244" t="str">
         <f>IF(E46=0,"",E46*E47/E43)</f>
         <v/>
       </c>
-      <c r="F48" s="249"/>
+      <c r="F48" s="244"/>
       <c r="G48" s="176"/>
       <c r="H48" s="176"/>
-      <c r="I48" s="253"/>
-      <c r="J48" s="253"/>
+      <c r="I48" s="245"/>
+      <c r="J48" s="245"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="70">
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="B46:D46"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="H43:J43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="B40:J40"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="H41:J41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="H42:J42"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="C9:J9"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="B18:J18"/>
     <mergeCell ref="B29:J29"/>
     <mergeCell ref="B30:F30"/>
@@ -14449,29 +14688,37 @@
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="E20:F20"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="H32:J32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="H33:J33"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="C9:J9"/>
-    <mergeCell ref="A1:W1"/>
-    <mergeCell ref="C3:J3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="B40:J40"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E47:F47"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1:W1" location="Sommaire!A1" display="Performances" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
@@ -14488,85 +14735,85 @@
     <tabColor theme="0" tint="-0.14999847407452621"/>
   </sheetPr>
   <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.41796875" defaultRowHeight="13.8" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" style="2" customWidth="1"/>
-    <col min="4" max="7" width="8.42578125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.42578125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" style="2" customWidth="1"/>
-    <col min="13" max="19" width="9.42578125" style="2" customWidth="1"/>
-    <col min="20" max="20" width="9.140625" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="1.41796875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.41796875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.41796875" style="2" customWidth="1"/>
+    <col min="4" max="7" width="8.41796875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.83984375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.41796875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13.68359375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10.578125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="8.68359375" style="2" customWidth="1"/>
+    <col min="13" max="19" width="9.41796875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="9.15625" style="2" customWidth="1"/>
+    <col min="21" max="16384" width="11.41796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="195" t="s">
+    <row r="1" spans="1:19" ht="17.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="183" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="195"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
-      <c r="H1" s="195"/>
-      <c r="I1" s="195"/>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-    </row>
-    <row r="2" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:19" ht="18" x14ac:dyDescent="0.25">
-      <c r="E3" s="189" t="s">
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
+      <c r="J1" s="183"/>
+      <c r="K1" s="183"/>
+      <c r="L1" s="183"/>
+      <c r="M1" s="183"/>
+      <c r="N1" s="183"/>
+      <c r="O1" s="183"/>
+      <c r="P1" s="183"/>
+      <c r="Q1" s="183"/>
+      <c r="R1" s="183"/>
+      <c r="S1" s="183"/>
+    </row>
+    <row r="2" spans="1:19" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="3" spans="1:19" ht="17.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="E3" s="211" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="190"/>
-      <c r="G3" s="190"/>
-      <c r="H3" s="191"/>
-      <c r="N3" s="184" t="s">
+      <c r="F3" s="212"/>
+      <c r="G3" s="212"/>
+      <c r="H3" s="213"/>
+      <c r="N3" s="206" t="s">
         <v>49</v>
       </c>
-      <c r="O3" s="185"/>
-      <c r="P3" s="185"/>
-      <c r="Q3" s="186"/>
-    </row>
-    <row r="4" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E4" s="187">
-        <v>20</v>
-      </c>
-      <c r="F4" s="187"/>
-      <c r="G4" s="188"/>
-      <c r="H4" s="188"/>
-      <c r="N4" s="181" t="s">
+      <c r="O3" s="207"/>
+      <c r="P3" s="207"/>
+      <c r="Q3" s="208"/>
+    </row>
+    <row r="4" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E4" s="209">
+        <v>12</v>
+      </c>
+      <c r="F4" s="209"/>
+      <c r="G4" s="210"/>
+      <c r="H4" s="210"/>
+      <c r="N4" s="203" t="s">
         <v>50</v>
       </c>
-      <c r="O4" s="182"/>
-      <c r="P4" s="183" t="s">
+      <c r="O4" s="204"/>
+      <c r="P4" s="205" t="s">
         <v>51</v>
       </c>
-      <c r="Q4" s="183"/>
-    </row>
-    <row r="5" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E5" s="198" t="s">
+      <c r="Q4" s="205"/>
+    </row>
+    <row r="5" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E5" s="186" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="198"/>
-      <c r="G5" s="198" t="s">
+      <c r="F5" s="186"/>
+      <c r="G5" s="186" t="s">
         <v>55</v>
       </c>
-      <c r="H5" s="198"/>
+      <c r="H5" s="186"/>
       <c r="N5" s="10" t="s">
         <v>59</v>
       </c>
@@ -14580,12 +14827,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="M6" s="10" t="s">
         <v>63</v>
       </c>
       <c r="N6" s="7">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="O6" s="8">
         <v>0</v>
@@ -14597,24 +14844,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="M7" s="10" t="s">
         <v>10</v>
       </c>
       <c r="N7" s="7">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="9">
         <f>IF(O7&gt;=O$6,N7-N$6,N7-N$6-1)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="10">
         <f>N7*60+O7-N$6*60-O$6-P7*60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="12"/>
       <c r="C8" s="22" t="s">
         <v>63</v>
@@ -14647,7 +14894,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="7">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="O8" s="8"/>
       <c r="P8" s="9">
@@ -14659,7 +14906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="21" t="s">
         <v>64</v>
       </c>
@@ -14695,7 +14942,7 @@
         <v>4</v>
       </c>
       <c r="N9" s="7">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="9">
@@ -14707,7 +14954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="16"/>
       <c r="C10" s="17"/>
       <c r="D10" s="22" t="s">
@@ -14735,112 +14982,112 @@
         <v>3</v>
       </c>
       <c r="N10" s="7">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="9">
         <f>IF(O10&gt;=O$6,N10-N$6,N10-N$6-1)</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q10" s="10">
         <f>N10*60+O10-N$6*60-O$6-P10*60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="179" t="s">
+    <row r="11" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="199" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="180"/>
+      <c r="C11" s="200"/>
       <c r="D11" s="23">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E11" s="23">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="F11" s="23">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G11" s="23">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H11" s="23">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="I11" s="23">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J11" s="28">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>7</v>
       </c>
       <c r="N11" s="7">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="O11" s="8"/>
       <c r="P11" s="9">
         <f>IF(O11&gt;=O$6,N11-N$6,N11-N$6-1)</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q11" s="10">
         <f>N11*60+O11-N$6*60-O$6-P11*60</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="211" t="s">
+    <row r="12" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="201" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="212"/>
+      <c r="C12" s="202"/>
       <c r="D12" s="23">
+        <v>3</v>
+      </c>
+      <c r="E12" s="23">
         <v>2</v>
       </c>
-      <c r="E12" s="23">
-        <v>3</v>
-      </c>
       <c r="F12" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="23">
+        <v>0</v>
+      </c>
+      <c r="H12" s="23">
+        <v>5</v>
+      </c>
+      <c r="I12" s="23">
         <v>2</v>
-      </c>
-      <c r="H12" s="23">
-        <v>1</v>
-      </c>
-      <c r="I12" s="23">
-        <v>1</v>
       </c>
       <c r="J12" s="26">
         <f>SUM(D12:I12)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="211" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="201" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="212"/>
+      <c r="C13" s="202"/>
       <c r="D13" s="24">
         <f t="shared" ref="D13:J13" si="0">IF(D11=0,0,D12/D11)</f>
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="E13" s="24">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>4.6511627906976744E-2</v>
       </c>
       <c r="F13" s="24">
         <f t="shared" si="0"/>
-        <v>9.0909090909090912E-2</v>
+        <v>0.10526315789473684</v>
       </c>
       <c r="G13" s="24">
         <f t="shared" si="0"/>
-        <v>0.22222222222222221</v>
+        <v>0</v>
       </c>
       <c r="H13" s="24">
         <f t="shared" si="0"/>
-        <v>0.125</v>
+        <v>0.14705882352941177</v>
       </c>
       <c r="I13" s="24">
         <f t="shared" si="0"/>
@@ -14848,51 +15095,51 @@
       </c>
       <c r="J13" s="27">
         <f t="shared" si="0"/>
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="L13" s="184" t="s">
+        <v>0.20895522388059701</v>
+      </c>
+      <c r="L13" s="206" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="185"/>
-      <c r="N13" s="185"/>
-      <c r="O13" s="185"/>
-      <c r="P13" s="185"/>
-      <c r="Q13" s="185"/>
-      <c r="R13" s="185"/>
-      <c r="S13" s="186"/>
-    </row>
-    <row r="14" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="179" t="s">
+      <c r="M13" s="207"/>
+      <c r="N13" s="207"/>
+      <c r="O13" s="207"/>
+      <c r="P13" s="207"/>
+      <c r="Q13" s="207"/>
+      <c r="R13" s="207"/>
+      <c r="S13" s="208"/>
+    </row>
+    <row r="14" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="199" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="180"/>
+      <c r="C14" s="200"/>
       <c r="D14" s="25">
         <f t="shared" ref="D14:J14" si="1">D11-D12</f>
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E14" s="25">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="F14" s="25">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G14" s="25">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H14" s="25">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="I14" s="25">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J14" s="29">
         <f t="shared" si="1"/>
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>0</v>
@@ -14919,106 +15166,114 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="23.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="L15" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M15" s="6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N15" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O15" s="6">
         <v>4</v>
       </c>
       <c r="P15" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q15" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R15" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S15" s="15">
         <f>SUM(L15:R15)</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="192" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="23.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" s="180" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="193"/>
-      <c r="D16" s="193"/>
-      <c r="E16" s="193"/>
-      <c r="F16" s="193"/>
-      <c r="G16" s="194"/>
-    </row>
-    <row r="17" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="210" t="s">
+      <c r="C16" s="181"/>
+      <c r="D16" s="181"/>
+      <c r="E16" s="181"/>
+      <c r="F16" s="181"/>
+      <c r="G16" s="182"/>
+    </row>
+    <row r="17" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="198" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="210"/>
-      <c r="D17" s="209" t="s">
+      <c r="C17" s="198"/>
+      <c r="D17" s="197" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="209"/>
-      <c r="F17" s="207" t="s">
+      <c r="E17" s="197"/>
+      <c r="F17" s="195" t="s">
         <v>68</v>
       </c>
-      <c r="G17" s="208"/>
-    </row>
-    <row r="18" spans="2:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="200">
+      <c r="G17" s="196"/>
+    </row>
+    <row r="18" spans="2:10" ht="27" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" s="188">
         <f>E4*60+G4</f>
-        <v>1200</v>
-      </c>
-      <c r="C18" s="206"/>
-      <c r="D18" s="204">
+        <v>720</v>
+      </c>
+      <c r="C18" s="194"/>
+      <c r="D18" s="192">
         <f>K9</f>
         <v>9</v>
       </c>
-      <c r="E18" s="205"/>
-      <c r="F18" s="201">
+      <c r="E18" s="193"/>
+      <c r="F18" s="189">
         <f>J14</f>
-        <v>38</v>
-      </c>
-      <c r="G18" s="202"/>
-    </row>
-    <row r="19" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="2:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="196" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="190"/>
+    </row>
+    <row r="19" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="20" spans="2:10" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" s="184" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="197"/>
-      <c r="D20" s="203">
+      <c r="C20" s="185"/>
+      <c r="D20" s="191">
         <f>ROUNDDOWN(H20,0)</f>
-        <v>4</v>
-      </c>
-      <c r="E20" s="203"/>
-      <c r="F20" s="199">
+        <v>2</v>
+      </c>
+      <c r="E20" s="191"/>
+      <c r="F20" s="187">
         <f>H20*60-D20*60</f>
-        <v>44.21052631578948</v>
-      </c>
-      <c r="G20" s="200"/>
-      <c r="H20" s="255">
+        <v>2.2641509433962312</v>
+      </c>
+      <c r="G20" s="188"/>
+      <c r="H20" s="179">
         <f>IF(F18=0,0,D18*B18/F18/60)</f>
-        <v>4.7368421052631584</v>
+        <v>2.0377358490566038</v>
       </c>
       <c r="I20" s="19" t="s">
         <v>65</v>
       </c>
       <c r="J20" s="19"/>
     </row>
-    <row r="21" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="N3:Q3"/>
+    <mergeCell ref="L13:S13"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="E3:H3"/>
     <mergeCell ref="B16:G16"/>
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="B20:C20"/>
@@ -15035,14 +15290,6 @@
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="L13:S13"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="E3:H3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1:S1" location="Sommaire!A1" display="Données Simulation 1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
@@ -15060,30 +15307,30 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.41796875" defaultRowHeight="13.8" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="31" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" style="31" customWidth="1"/>
-    <col min="3" max="9" width="7.42578125" style="31" customWidth="1"/>
-    <col min="10" max="16384" width="11.42578125" style="31"/>
+    <col min="1" max="1" width="2.41796875" style="31" customWidth="1"/>
+    <col min="2" max="2" width="14.68359375" style="31" customWidth="1"/>
+    <col min="3" max="9" width="7.41796875" style="31" customWidth="1"/>
+    <col min="10" max="16384" width="11.41796875" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="217" t="s">
+    <row r="1" spans="1:10" ht="17.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="218" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="217"/>
-      <c r="C1" s="217"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
-      <c r="F1" s="217"/>
-      <c r="G1" s="217"/>
-      <c r="H1" s="217"/>
-      <c r="I1" s="217"/>
-      <c r="J1" s="217"/>
-    </row>
-    <row r="2" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="218"/>
+      <c r="C1" s="218"/>
+      <c r="D1" s="218"/>
+      <c r="E1" s="218"/>
+      <c r="F1" s="218"/>
+      <c r="G1" s="218"/>
+      <c r="H1" s="218"/>
+      <c r="I1" s="218"/>
+      <c r="J1" s="218"/>
+    </row>
+    <row r="2" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="3" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="17"/>
       <c r="C3" s="22" t="s">
         <v>0</v>
@@ -15107,29 +15354,29 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="93" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="24">
         <f>'Données Simulation 1'!D13</f>
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="D4" s="24">
         <f>'Données Simulation 1'!E13</f>
-        <v>0.5</v>
+        <v>4.6511627906976744E-2</v>
       </c>
       <c r="E4" s="24">
         <f>'Données Simulation 1'!F13</f>
-        <v>9.0909090909090912E-2</v>
+        <v>0.10526315789473684</v>
       </c>
       <c r="F4" s="24">
         <f>'Données Simulation 1'!G13</f>
-        <v>0.22222222222222221</v>
+        <v>0</v>
       </c>
       <c r="G4" s="24">
         <f>'Données Simulation 1'!H13</f>
-        <v>0.125</v>
+        <v>0.14705882352941177</v>
       </c>
       <c r="H4" s="24">
         <f>'Données Simulation 1'!I13</f>
@@ -15137,7 +15384,7 @@
       </c>
       <c r="I4" s="24">
         <f>'Données Simulation 1'!J13</f>
-        <v>0.20833333333333334</v>
+        <v>0.20895522388059701</v>
       </c>
     </row>
   </sheetData>
@@ -15159,82 +15406,82 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:W7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.41796875" defaultRowHeight="13.8" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.41796875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.15625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.83984375" style="2" customWidth="1"/>
     <col min="5" max="5" width="12" style="2" customWidth="1"/>
     <col min="6" max="6" width="9" style="2" customWidth="1"/>
-    <col min="7" max="7" width="7.28515625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="6.85546875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="5.5703125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="2"/>
+    <col min="7" max="7" width="7.26171875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="6.83984375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="5.578125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9.15625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9.68359375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="9.15625" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="11.41796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="195" t="s">
+    <row r="1" spans="1:23" ht="17.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="183" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="195"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
-      <c r="H1" s="195"/>
-      <c r="I1" s="195"/>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
-      <c r="V1" s="195"/>
-      <c r="W1" s="195"/>
-    </row>
-    <row r="2" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="218" t="s">
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
+      <c r="J1" s="183"/>
+      <c r="K1" s="183"/>
+      <c r="L1" s="183"/>
+      <c r="M1" s="183"/>
+      <c r="N1" s="183"/>
+      <c r="O1" s="183"/>
+      <c r="P1" s="183"/>
+      <c r="Q1" s="183"/>
+      <c r="R1" s="183"/>
+      <c r="S1" s="183"/>
+      <c r="T1" s="183"/>
+      <c r="U1" s="183"/>
+      <c r="V1" s="183"/>
+      <c r="W1" s="183"/>
+    </row>
+    <row r="2" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="3" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C3" s="219" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="218"/>
-      <c r="E3" s="218"/>
-      <c r="F3" s="218"/>
-      <c r="G3" s="218"/>
-      <c r="H3" s="218"/>
-      <c r="I3" s="218"/>
-      <c r="J3" s="218"/>
-    </row>
-    <row r="4" spans="1:23" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="220" t="s">
+      <c r="D3" s="219"/>
+      <c r="E3" s="219"/>
+      <c r="F3" s="219"/>
+      <c r="G3" s="219"/>
+      <c r="H3" s="219"/>
+      <c r="I3" s="219"/>
+      <c r="J3" s="219"/>
+    </row>
+    <row r="4" spans="1:23" ht="33.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C4" s="221" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="221"/>
-      <c r="E4" s="219" t="s">
+      <c r="D4" s="222"/>
+      <c r="E4" s="220" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="219"/>
-      <c r="G4" s="219" t="s">
+      <c r="F4" s="220"/>
+      <c r="G4" s="220" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="219"/>
-      <c r="I4" s="219" t="s">
+      <c r="H4" s="220"/>
+      <c r="I4" s="220" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="219"/>
-    </row>
-    <row r="5" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J4" s="220"/>
+    </row>
+    <row r="5" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="35" t="s">
         <v>42</v>
       </c>
@@ -15267,7 +15514,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="41" t="s">
         <v>70</v>
       </c>
@@ -15300,29 +15547,29 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="47" t="s">
         <v>76</v>
       </c>
       <c r="C7" s="47">
         <f>'Données Simulation 1'!H20</f>
-        <v>4.7368421052631584</v>
+        <v>2.0377358490566038</v>
       </c>
       <c r="D7" s="48">
         <f>10+C7</f>
-        <v>14.736842105263158</v>
+        <v>12.037735849056604</v>
       </c>
       <c r="E7" s="47">
         <f>('Données Simulation 1'!P11*60+'Données Simulation 1'!Q11)/60</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F7" s="49">
         <f>60+5*E7</f>
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="G7" s="50">
         <f>'Données Simulation 1'!J13</f>
-        <v>0.20833333333333334</v>
+        <v>0.20895522388059701</v>
       </c>
       <c r="H7" s="51">
         <f>MAX(100-G7*100*5,0)</f>
@@ -15330,11 +15577,11 @@
       </c>
       <c r="I7" s="51">
         <f>'Données Simulation 1'!S15</f>
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J7" s="52">
         <f>8+I7*2/5</f>
-        <v>20.8</v>
+        <v>17.600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -15361,59 +15608,59 @@
     <tabColor rgb="FF0066CC"/>
   </sheetPr>
   <dimension ref="A1:P62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.41796875" defaultRowHeight="13.8" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.41796875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.41796875" style="2" customWidth="1"/>
     <col min="3" max="8" width="9" style="2" customWidth="1"/>
-    <col min="9" max="9" width="7.42578125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="8.42578125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="2"/>
+    <col min="9" max="9" width="7.41796875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9.15625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="8.41796875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.15625" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="11.41796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="195" t="s">
+    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="183" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="195"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
-      <c r="H1" s="195"/>
-      <c r="I1" s="195"/>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-    </row>
-    <row r="2" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
+      <c r="J1" s="183"/>
+      <c r="K1" s="183"/>
+      <c r="L1" s="183"/>
+      <c r="M1" s="183"/>
+      <c r="N1" s="183"/>
+      <c r="O1" s="183"/>
+      <c r="P1" s="183"/>
+    </row>
+    <row r="2" spans="1:16" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="79" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="223">
+      <c r="C3" s="224">
         <f>IF(ISNA(VLOOKUP(C38,B40:C62,2,FALSE)),0,VLOOKUP(C38,B40:C62,2,FALSE))</f>
         <v>600000</v>
       </c>
-      <c r="D3" s="223"/>
+      <c r="D3" s="224"/>
       <c r="E3" s="81" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="5" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="6" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="12"/>
       <c r="C6" s="22" t="s">
         <v>0</v>
@@ -15434,7 +15681,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="75" t="s">
         <v>81</v>
       </c>
@@ -15463,17 +15710,17 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="75" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="222">
+      <c r="C8" s="223">
         <f>2000*3600</f>
         <v>7200000</v>
       </c>
-      <c r="D8" s="222"/>
-    </row>
-    <row r="9" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D8" s="223"/>
+    </row>
+    <row r="9" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="77" t="s">
         <v>83</v>
       </c>
@@ -15502,52 +15749,52 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="11" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="76" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="75" t="s">
         <v>90</v>
       </c>
       <c r="C12" s="75">
         <f>'Données Simulation 1'!D11</f>
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D12" s="75">
         <f>'Données Simulation 1'!E11</f>
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="E12" s="75">
         <f>'Données Simulation 1'!F11</f>
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F12" s="75">
         <f>'Données Simulation 1'!G11</f>
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G12" s="75">
         <f>'Données Simulation 1'!H11</f>
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="H12" s="75">
         <f>'Données Simulation 1'!I11</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B13" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="222">
+      <c r="C13" s="223">
         <f>'Données Simulation 1'!B18</f>
-        <v>1200</v>
-      </c>
-      <c r="D13" s="222"/>
-    </row>
-    <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>720</v>
+      </c>
+      <c r="D13" s="223"/>
+    </row>
+    <row r="14" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" s="75" t="s">
         <v>91</v>
       </c>
@@ -15558,7 +15805,7 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
     </row>
-    <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="75" t="s">
         <v>92</v>
       </c>
@@ -15587,7 +15834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="78" t="s">
         <v>84</v>
       </c>
@@ -15616,37 +15863,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="18" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="19" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="84" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="183" t="s">
+    <row r="20" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="21" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="22" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="23" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="24" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="25" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="26" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="27" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="28" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="29" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="30" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="31" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="32" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="33" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="34" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="35" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="36" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="37" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="205" t="s">
         <v>87</v>
       </c>
-      <c r="C37" s="183"/>
-    </row>
-    <row r="38" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="205"/>
+    </row>
+    <row r="38" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" s="80" t="s">
         <v>80</v>
       </c>
@@ -15655,7 +15902,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="2:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B39" s="14" t="s">
         <v>64</v>
       </c>
@@ -15663,7 +15910,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B40" s="83">
         <v>8</v>
       </c>
@@ -15671,7 +15918,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="41" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="83">
         <f>B40+1</f>
         <v>9</v>
@@ -15680,7 +15927,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="42" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="83">
         <f t="shared" ref="B42:B62" si="3">B41+1</f>
         <v>10</v>
@@ -15689,7 +15936,7 @@
         <v>600000</v>
       </c>
     </row>
-    <row r="43" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="83">
         <f>B42+1</f>
         <v>11</v>
@@ -15698,7 +15945,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="44" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="83">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -15707,7 +15954,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="45" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="83">
         <f t="shared" si="3"/>
         <v>13</v>
@@ -15716,7 +15963,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="83">
         <f t="shared" si="3"/>
         <v>14</v>
@@ -15725,7 +15972,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="83">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -15734,7 +15981,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="83">
         <f t="shared" si="3"/>
         <v>16</v>
@@ -15743,7 +15990,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="83">
         <f t="shared" si="3"/>
         <v>17</v>
@@ -15752,7 +15999,7 @@
         <v>1200000</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="83">
         <f t="shared" si="3"/>
         <v>18</v>
@@ -15761,7 +16008,7 @@
         <v>1200000</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="83">
         <f t="shared" si="3"/>
         <v>19</v>
@@ -15770,7 +16017,7 @@
         <v>1200000</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="83">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -15779,7 +16026,7 @@
         <v>1200000</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="83">
         <f t="shared" si="3"/>
         <v>21</v>
@@ -15788,7 +16035,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="83">
         <f t="shared" si="3"/>
         <v>22</v>
@@ -15797,7 +16044,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="83">
         <f t="shared" si="3"/>
         <v>23</v>
@@ -15806,7 +16053,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="83">
         <f t="shared" si="3"/>
         <v>24</v>
@@ -15815,7 +16062,7 @@
         <v>1400000</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="83">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -15824,7 +16071,7 @@
         <v>1700000</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="83">
         <f t="shared" si="3"/>
         <v>26</v>
@@ -15833,7 +16080,7 @@
         <v>1700000</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="83">
         <f t="shared" si="3"/>
         <v>27</v>
@@ -15842,7 +16089,7 @@
         <v>1700000</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="83">
         <f t="shared" si="3"/>
         <v>28</v>
@@ -15851,7 +16098,7 @@
         <v>1700000</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="83">
         <f t="shared" si="3"/>
         <v>29</v>
@@ -15860,7 +16107,7 @@
         <v>1700000</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="83">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -15888,45 +16135,93 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00B2D355-A839-4DBF-98BC-3CB7FDA3EBF4}">
+  <dimension ref="C4:E10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="4" spans="3:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="D4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6" spans="3:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="7" spans="3:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="3:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="3:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="3:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="C10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="B1:O11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.41796875" defaultRowHeight="13.8" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.41796875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22.15625" style="2" customWidth="1"/>
     <col min="3" max="8" width="7" style="2" customWidth="1"/>
-    <col min="9" max="9" width="7.42578125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="8.42578125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="11.42578125" style="2"/>
+    <col min="9" max="9" width="7.41796875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9.15625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="8.41796875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.15625" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="11.41796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="195" t="s">
+    <row r="1" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="183" t="s">
         <v>131</v>
       </c>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
-      <c r="H1" s="195"/>
-      <c r="I1" s="195"/>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-    </row>
-    <row r="2" spans="2:15" ht="36.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
+      <c r="J1" s="183"/>
+      <c r="K1" s="183"/>
+      <c r="L1" s="183"/>
+      <c r="M1" s="183"/>
+      <c r="N1" s="183"/>
+      <c r="O1" s="183"/>
+    </row>
+    <row r="2" spans="2:15" ht="36.75" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="3" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="4" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="5" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="88" t="s">
         <v>133</v>
       </c>
@@ -15949,134 +16244,146 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="74"/>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-    </row>
-    <row r="7" spans="2:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="74">
+        <v>7.5</v>
+      </c>
+      <c r="D6" s="74">
+        <v>16.5</v>
+      </c>
+      <c r="E6" s="74">
+        <v>18.5</v>
+      </c>
+      <c r="F6" s="74">
+        <v>9.75</v>
+      </c>
+      <c r="G6" s="74">
+        <v>15</v>
+      </c>
+      <c r="H6" s="74">
+        <v>11.75</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="147" t="s">
         <v>121</v>
       </c>
       <c r="C7" s="89">
         <f>IF('Données Simulation 1'!D9=0,0,'Données Simulation 1'!D14/'Données Simulation 1'!D9)</f>
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D7" s="89">
         <f>IF('Données Simulation 1'!E9=0,0,'Données Simulation 1'!E14/'Données Simulation 1'!E9)</f>
-        <v>1.5</v>
+        <v>20.5</v>
       </c>
       <c r="E7" s="89">
         <f>IF('Données Simulation 1'!F9=0,0,'Données Simulation 1'!F14/'Données Simulation 1'!F9)</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F7" s="89">
         <f>IF('Données Simulation 1'!G9=0,0,'Données Simulation 1'!G14/'Données Simulation 1'!G9)</f>
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G7" s="89">
         <f>IF('Données Simulation 1'!H9=0,0,'Données Simulation 1'!H14/'Données Simulation 1'!H9)</f>
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="H7" s="89">
         <f>IF('Données Simulation 1'!I9=0,0,'Données Simulation 1'!I14/'Données Simulation 1'!I9)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="75" t="s">
         <v>93</v>
       </c>
       <c r="C8" s="141">
         <f t="shared" ref="C8:H8" si="0">C7*C6</f>
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="D8" s="141">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>338.25</v>
       </c>
       <c r="E8" s="141">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>314.5</v>
       </c>
       <c r="F8" s="141">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>253.5</v>
       </c>
       <c r="G8" s="141">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>435</v>
       </c>
       <c r="H8" s="141">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>164.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="90" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="142">
         <f>'Données Simulation 1'!$B$18</f>
-        <v>1200</v>
+        <v>720</v>
       </c>
       <c r="D9" s="142">
         <f>'Données Simulation 1'!$B$18</f>
-        <v>1200</v>
+        <v>720</v>
       </c>
       <c r="E9" s="142">
         <f>'Données Simulation 1'!$B$18</f>
-        <v>1200</v>
+        <v>720</v>
       </c>
       <c r="F9" s="142">
         <f>'Données Simulation 1'!$B$18</f>
-        <v>1200</v>
+        <v>720</v>
       </c>
       <c r="G9" s="142">
         <f>'Données Simulation 1'!$B$18</f>
-        <v>1200</v>
+        <v>720</v>
       </c>
       <c r="H9" s="142">
         <f>'Données Simulation 1'!$B$18</f>
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="91" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="92">
         <f t="shared" ref="C10:H10" si="1">IF(C9=0,0,C8/C9)</f>
-        <v>0</v>
+        <v>0.22916666666666666</v>
       </c>
       <c r="D10" s="92">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.46979166666666666</v>
       </c>
       <c r="E10" s="92">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.43680555555555556</v>
       </c>
       <c r="F10" s="92">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35208333333333336</v>
       </c>
       <c r="G10" s="92">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.60416666666666663</v>
       </c>
       <c r="H10" s="92">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>0.22847222222222222</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
   <sheetProtection sheet="1"/>
   <mergeCells count="1">
@@ -16091,34 +16398,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.41796875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" style="123" customWidth="1"/>
-    <col min="2" max="6" width="17.140625" style="123" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="123" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" style="94" customWidth="1"/>
-    <col min="9" max="16384" width="11.42578125" style="123"/>
+    <col min="1" max="1" width="4.26171875" style="123" customWidth="1"/>
+    <col min="2" max="6" width="17.15625" style="123" customWidth="1"/>
+    <col min="7" max="7" width="13.41796875" style="123" customWidth="1"/>
+    <col min="8" max="8" width="7.68359375" style="94" customWidth="1"/>
+    <col min="9" max="16384" width="11.41796875" style="123"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="195" t="s">
+    <row r="1" spans="1:8" ht="17.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="183" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="195"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
-      <c r="H1" s="195"/>
-    </row>
-    <row r="3" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
+    </row>
+    <row r="3" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="124" t="s">
         <v>58</v>
       </c>
@@ -16141,7 +16448,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -16153,8 +16460,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="9" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="6" spans="1:8" ht="28.2" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="172" t="s">
         <v>6</v>
       </c>
@@ -16168,7 +16475,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="171"/>
       <c r="C7" s="171"/>
       <c r="D7" s="171"/>
@@ -16187,88 +16494,88 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:AY25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.41796875" defaultRowHeight="13.8" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" style="112" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" style="2" customWidth="1"/>
-    <col min="6" max="7" width="3.42578125" style="112" customWidth="1"/>
-    <col min="8" max="9" width="3.42578125" style="2" customWidth="1"/>
-    <col min="10" max="11" width="3.28515625" style="121" customWidth="1"/>
-    <col min="12" max="13" width="3.42578125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="3.42578125" style="112" customWidth="1"/>
-    <col min="15" max="17" width="3.42578125" style="2" customWidth="1"/>
-    <col min="18" max="19" width="3.28515625" style="121" customWidth="1"/>
-    <col min="20" max="25" width="3.42578125" style="2" customWidth="1"/>
-    <col min="26" max="27" width="3.28515625" style="121" customWidth="1"/>
-    <col min="28" max="33" width="3.42578125" style="2" customWidth="1"/>
-    <col min="34" max="35" width="3.28515625" style="121" customWidth="1"/>
-    <col min="36" max="41" width="3.42578125" style="2" customWidth="1"/>
-    <col min="42" max="43" width="3.28515625" style="2" customWidth="1"/>
-    <col min="44" max="47" width="3.42578125" style="2" customWidth="1"/>
-    <col min="48" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="1.15625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.15625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.15625" style="112" customWidth="1"/>
+    <col min="4" max="4" width="9.68359375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="4.68359375" style="2" customWidth="1"/>
+    <col min="6" max="7" width="3.41796875" style="112" customWidth="1"/>
+    <col min="8" max="9" width="3.41796875" style="2" customWidth="1"/>
+    <col min="10" max="11" width="3.26171875" style="121" customWidth="1"/>
+    <col min="12" max="13" width="3.41796875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="3.41796875" style="112" customWidth="1"/>
+    <col min="15" max="17" width="3.41796875" style="2" customWidth="1"/>
+    <col min="18" max="19" width="3.26171875" style="121" customWidth="1"/>
+    <col min="20" max="25" width="3.41796875" style="2" customWidth="1"/>
+    <col min="26" max="27" width="3.26171875" style="121" customWidth="1"/>
+    <col min="28" max="33" width="3.41796875" style="2" customWidth="1"/>
+    <col min="34" max="35" width="3.26171875" style="121" customWidth="1"/>
+    <col min="36" max="41" width="3.41796875" style="2" customWidth="1"/>
+    <col min="42" max="43" width="3.26171875" style="2" customWidth="1"/>
+    <col min="44" max="47" width="3.41796875" style="2" customWidth="1"/>
+    <col min="48" max="16384" width="11.41796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="195" t="s">
+    <row r="1" spans="1:51" ht="17.7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="183" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="195"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="195"/>
-      <c r="F1" s="195"/>
-      <c r="G1" s="195"/>
-      <c r="H1" s="195"/>
-      <c r="I1" s="195"/>
-      <c r="J1" s="195"/>
-      <c r="K1" s="195"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
-      <c r="R1" s="195"/>
-      <c r="S1" s="195"/>
-      <c r="T1" s="195"/>
-      <c r="U1" s="195"/>
-      <c r="V1" s="195"/>
-      <c r="W1" s="195"/>
-      <c r="X1" s="195"/>
-      <c r="Y1" s="195"/>
-      <c r="Z1" s="195"/>
-      <c r="AA1" s="195"/>
-      <c r="AB1" s="195"/>
-      <c r="AC1" s="195"/>
-      <c r="AD1" s="195"/>
-      <c r="AE1" s="195"/>
-      <c r="AF1" s="195"/>
-      <c r="AG1" s="195"/>
-      <c r="AH1" s="195"/>
-      <c r="AI1" s="195"/>
-      <c r="AJ1" s="195"/>
-      <c r="AK1" s="195"/>
-      <c r="AL1" s="195"/>
-      <c r="AM1" s="195"/>
-      <c r="AN1" s="195"/>
-      <c r="AO1" s="195"/>
-      <c r="AP1" s="195"/>
-      <c r="AQ1" s="195"/>
-      <c r="AR1" s="195"/>
-      <c r="AS1" s="195"/>
-      <c r="AT1" s="195"/>
-      <c r="AU1" s="195"/>
-    </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
+      <c r="J1" s="183"/>
+      <c r="K1" s="183"/>
+      <c r="L1" s="183"/>
+      <c r="M1" s="183"/>
+      <c r="N1" s="183"/>
+      <c r="O1" s="183"/>
+      <c r="P1" s="183"/>
+      <c r="Q1" s="183"/>
+      <c r="R1" s="183"/>
+      <c r="S1" s="183"/>
+      <c r="T1" s="183"/>
+      <c r="U1" s="183"/>
+      <c r="V1" s="183"/>
+      <c r="W1" s="183"/>
+      <c r="X1" s="183"/>
+      <c r="Y1" s="183"/>
+      <c r="Z1" s="183"/>
+      <c r="AA1" s="183"/>
+      <c r="AB1" s="183"/>
+      <c r="AC1" s="183"/>
+      <c r="AD1" s="183"/>
+      <c r="AE1" s="183"/>
+      <c r="AF1" s="183"/>
+      <c r="AG1" s="183"/>
+      <c r="AH1" s="183"/>
+      <c r="AI1" s="183"/>
+      <c r="AJ1" s="183"/>
+      <c r="AK1" s="183"/>
+      <c r="AL1" s="183"/>
+      <c r="AM1" s="183"/>
+      <c r="AN1" s="183"/>
+      <c r="AO1" s="183"/>
+      <c r="AP1" s="183"/>
+      <c r="AQ1" s="183"/>
+      <c r="AR1" s="183"/>
+      <c r="AS1" s="183"/>
+      <c r="AT1" s="183"/>
+      <c r="AU1" s="183"/>
+    </row>
+    <row r="2" spans="1:51" x14ac:dyDescent="0.55000000000000004">
       <c r="C2" s="2"/>
       <c r="E2" s="149" t="s">
         <v>128</v>
@@ -16296,45 +16603,45 @@
       <c r="AN2" s="121"/>
       <c r="AO2" s="121"/>
     </row>
-    <row r="3" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:51" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="I3" s="112"/>
-      <c r="J3" s="232" t="s">
+      <c r="J3" s="236" t="s">
         <v>99</v>
       </c>
-      <c r="K3" s="232"/>
+      <c r="K3" s="236"/>
       <c r="L3" s="112"/>
       <c r="M3" s="112"/>
       <c r="N3" s="2"/>
       <c r="P3" s="121"/>
       <c r="Q3" s="121"/>
-      <c r="R3" s="232" t="s">
+      <c r="R3" s="236" t="s">
         <v>99</v>
       </c>
-      <c r="S3" s="232"/>
+      <c r="S3" s="236"/>
       <c r="T3" s="112"/>
       <c r="X3" s="121"/>
       <c r="Y3" s="121"/>
-      <c r="Z3" s="232" t="s">
+      <c r="Z3" s="236" t="s">
         <v>99</v>
       </c>
-      <c r="AA3" s="232"/>
+      <c r="AA3" s="236"/>
       <c r="AF3" s="121"/>
       <c r="AG3" s="121"/>
-      <c r="AH3" s="232" t="s">
+      <c r="AH3" s="236" t="s">
         <v>99</v>
       </c>
-      <c r="AI3" s="232"/>
+      <c r="AI3" s="236"/>
       <c r="AN3" s="121"/>
       <c r="AO3" s="121"/>
-      <c r="AP3" s="232" t="s">
+      <c r="AP3" s="236" t="s">
         <v>99</v>
       </c>
-      <c r="AQ3" s="232"/>
-    </row>
-    <row r="4" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AQ3" s="236"/>
+    </row>
+    <row r="4" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="166" t="s">
         <v>63</v>
       </c>
@@ -16350,8 +16657,8 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="I4" s="112"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="234"/>
+      <c r="J4" s="227"/>
+      <c r="K4" s="228"/>
       <c r="L4" s="112"/>
       <c r="M4" s="112">
         <f t="shared" ref="M4:M10" si="0">M5+2</f>
@@ -16364,8 +16671,8 @@
         <v>16</v>
       </c>
       <c r="Q4" s="121"/>
-      <c r="R4" s="233"/>
-      <c r="S4" s="234"/>
+      <c r="R4" s="227"/>
+      <c r="S4" s="228"/>
       <c r="T4" s="112"/>
       <c r="U4" s="112">
         <f t="shared" ref="U4:U10" si="2">U5+2</f>
@@ -16378,8 +16685,8 @@
         <v>16</v>
       </c>
       <c r="Y4" s="121"/>
-      <c r="Z4" s="233"/>
-      <c r="AA4" s="234"/>
+      <c r="Z4" s="227"/>
+      <c r="AA4" s="228"/>
       <c r="AC4" s="112">
         <f t="shared" ref="AC4:AC10" si="4">AC5+2</f>
         <v>15</v>
@@ -16391,8 +16698,8 @@
         <v>16</v>
       </c>
       <c r="AG4" s="121"/>
-      <c r="AH4" s="233"/>
-      <c r="AI4" s="234"/>
+      <c r="AH4" s="227"/>
+      <c r="AI4" s="228"/>
       <c r="AK4" s="112">
         <f t="shared" ref="AK4:AK10" si="6">AK5+2</f>
         <v>15</v>
@@ -16404,8 +16711,8 @@
         <v>16</v>
       </c>
       <c r="AO4" s="121"/>
-      <c r="AP4" s="233"/>
-      <c r="AQ4" s="234"/>
+      <c r="AP4" s="227"/>
+      <c r="AQ4" s="228"/>
       <c r="AS4" s="112">
         <f t="shared" ref="AS4:AS10" si="8">AS5+2</f>
         <v>15</v>
@@ -16417,24 +16724,24 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="238" t="s">
+    <row r="5" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="225" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="150">
         <f>'Données Simulation 1'!P7*60+'Données Simulation 1'!Q7</f>
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D5" s="161">
         <f>C5-D4</f>
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="E5" s="153" t="s">
         <v>124</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="228"/>
-      <c r="H5" s="228"/>
+      <c r="G5" s="239"/>
+      <c r="H5" s="239"/>
       <c r="I5" s="112">
         <f>I6+2</f>
         <v>3</v>
@@ -16535,23 +16842,23 @@
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="AW5" s="230"/>
-      <c r="AX5" s="230"/>
-      <c r="AY5" s="230"/>
-    </row>
-    <row r="6" spans="1:51" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="239"/>
+      <c r="AW5" s="240"/>
+      <c r="AX5" s="240"/>
+      <c r="AY5" s="240"/>
+    </row>
+    <row r="6" spans="1:51" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B6" s="226"/>
       <c r="C6" s="154"/>
       <c r="D6" s="151">
         <f>TRG!F6</f>
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="E6" s="152" t="s">
         <v>28</v>
       </c>
       <c r="F6" s="2"/>
-      <c r="G6" s="228"/>
-      <c r="H6" s="228"/>
+      <c r="G6" s="239"/>
+      <c r="H6" s="239"/>
       <c r="I6" s="112">
         <v>1</v>
       </c>
@@ -16644,8 +16951,8 @@
       </c>
       <c r="AY6" s="112"/>
     </row>
-    <row r="7" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="238" t="s">
+    <row r="7" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="225" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="150">
@@ -16654,7 +16961,7 @@
       </c>
       <c r="D7" s="162">
         <f>C7-C5-D6</f>
-        <v>180</v>
+        <v>230.25</v>
       </c>
       <c r="E7" s="153" t="s">
         <v>124</v>
@@ -16730,12 +17037,12 @@
       </c>
       <c r="AY7" s="112"/>
     </row>
-    <row r="8" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="239"/>
+    <row r="8" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="226"/>
       <c r="C8" s="155"/>
       <c r="D8" s="151">
         <f>TRG!D6</f>
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="E8" s="152" t="s">
         <v>28</v>
@@ -16811,8 +17118,8 @@
       </c>
       <c r="AY8" s="112"/>
     </row>
-    <row r="9" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="238" t="s">
+    <row r="9" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="225" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="150">
@@ -16821,7 +17128,7 @@
       </c>
       <c r="D9" s="163">
         <f>C9-C7-D8</f>
-        <v>120</v>
+        <v>103.5</v>
       </c>
       <c r="E9" s="153" t="s">
         <v>124</v>
@@ -16897,12 +17204,12 @@
       </c>
       <c r="AY9" s="112"/>
     </row>
-    <row r="10" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="239"/>
+    <row r="10" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="226"/>
       <c r="C10" s="155"/>
       <c r="D10" s="151">
         <f>TRG!H6</f>
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="E10" s="152" t="s">
         <v>28</v>
@@ -16978,17 +17285,17 @@
       </c>
       <c r="AY10" s="112"/>
     </row>
-    <row r="11" spans="1:51" s="119" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="238" t="s">
+    <row r="11" spans="1:51" s="119" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="225" t="s">
         <v>123</v>
       </c>
       <c r="C11" s="150">
         <f>'Données Simulation 1'!P10*60+'Données Simulation 1'!Q10</f>
-        <v>660</v>
+        <v>480</v>
       </c>
       <c r="D11" s="164">
         <f>C11-C9-D10</f>
-        <v>240</v>
+        <v>48.25</v>
       </c>
       <c r="E11" s="153" t="s">
         <v>124</v>
@@ -17002,8 +17309,8 @@
         <v>2</v>
       </c>
       <c r="Q11" s="121"/>
-      <c r="R11" s="229"/>
-      <c r="S11" s="229"/>
+      <c r="R11" s="234"/>
+      <c r="S11" s="234"/>
       <c r="U11" s="112">
         <v>1</v>
       </c>
@@ -17013,8 +17320,8 @@
         <v>2</v>
       </c>
       <c r="Y11" s="121"/>
-      <c r="Z11" s="229"/>
-      <c r="AA11" s="229"/>
+      <c r="Z11" s="234"/>
+      <c r="AA11" s="234"/>
       <c r="AC11" s="112">
         <v>1</v>
       </c>
@@ -17024,8 +17331,8 @@
         <v>2</v>
       </c>
       <c r="AG11" s="121"/>
-      <c r="AH11" s="229"/>
-      <c r="AI11" s="229"/>
+      <c r="AH11" s="234"/>
+      <c r="AI11" s="234"/>
       <c r="AK11" s="112">
         <v>1</v>
       </c>
@@ -17035,8 +17342,8 @@
         <v>2</v>
       </c>
       <c r="AO11" s="121"/>
-      <c r="AP11" s="229"/>
-      <c r="AQ11" s="229"/>
+      <c r="AP11" s="234"/>
+      <c r="AQ11" s="234"/>
       <c r="AS11" s="112">
         <v>1</v>
       </c>
@@ -17046,12 +17353,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:51" s="119" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="239"/>
+    <row r="12" spans="1:51" s="119" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="226"/>
       <c r="C12" s="155"/>
       <c r="D12" s="151">
         <f>TRG!G6</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E12" s="152" t="s">
         <v>28</v>
@@ -17059,109 +17366,109 @@
       <c r="J12" s="120"/>
       <c r="K12" s="120"/>
       <c r="M12" s="112"/>
-      <c r="N12" s="224">
+      <c r="N12" s="229">
         <f>'Données Simulation 1'!O15</f>
         <v>4</v>
       </c>
-      <c r="O12" s="225"/>
+      <c r="O12" s="230"/>
       <c r="P12" s="121"/>
       <c r="Q12" s="121"/>
       <c r="R12" s="120"/>
       <c r="S12" s="120"/>
       <c r="U12" s="112"/>
-      <c r="V12" s="224">
+      <c r="V12" s="229">
         <f>'Données Simulation 1'!M15</f>
-        <v>8</v>
-      </c>
-      <c r="W12" s="225"/>
+        <v>4</v>
+      </c>
+      <c r="W12" s="230"/>
       <c r="X12" s="121"/>
       <c r="Y12" s="121"/>
       <c r="Z12" s="120"/>
       <c r="AA12" s="120"/>
       <c r="AC12" s="112"/>
-      <c r="AD12" s="224">
+      <c r="AD12" s="229">
         <f>'Données Simulation 1'!Q15</f>
-        <v>4</v>
-      </c>
-      <c r="AE12" s="225"/>
+        <v>2</v>
+      </c>
+      <c r="AE12" s="230"/>
       <c r="AF12" s="121"/>
       <c r="AG12" s="121"/>
       <c r="AH12" s="120"/>
       <c r="AI12" s="120"/>
       <c r="AK12" s="112"/>
-      <c r="AL12" s="224">
+      <c r="AL12" s="229">
         <f>'Données Simulation 1'!P15</f>
-        <v>3</v>
-      </c>
-      <c r="AM12" s="225"/>
+        <v>8</v>
+      </c>
+      <c r="AM12" s="230"/>
       <c r="AN12" s="121"/>
       <c r="AO12" s="121"/>
       <c r="AP12" s="120"/>
       <c r="AQ12" s="120"/>
       <c r="AS12" s="112"/>
-      <c r="AT12" s="224">
+      <c r="AT12" s="229">
         <f>'Données Simulation 1'!R15</f>
-        <v>4</v>
-      </c>
-      <c r="AU12" s="225"/>
+        <v>2</v>
+      </c>
+      <c r="AU12" s="230"/>
       <c r="AV12" s="112"/>
     </row>
-    <row r="13" spans="1:51" s="119" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="238" t="s">
+    <row r="13" spans="1:51" s="119" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="225" t="s">
         <v>122</v>
       </c>
       <c r="C13" s="150">
         <f>'Données Simulation 1'!P11*60+'Données Simulation 1'!Q11</f>
-        <v>900</v>
+        <v>540</v>
       </c>
       <c r="D13" s="165">
         <f>C13-C11-D12</f>
-        <v>240</v>
+        <v>45</v>
       </c>
       <c r="E13" s="153" t="s">
         <v>124</v>
       </c>
       <c r="J13" s="120"/>
       <c r="K13" s="120"/>
-      <c r="N13" s="231" t="s">
+      <c r="N13" s="235" t="s">
         <v>100</v>
       </c>
-      <c r="O13" s="231"/>
+      <c r="O13" s="235"/>
       <c r="P13" s="121"/>
       <c r="Q13" s="121"/>
       <c r="R13" s="120"/>
       <c r="S13" s="120"/>
-      <c r="V13" s="231" t="s">
+      <c r="V13" s="235" t="s">
         <v>100</v>
       </c>
-      <c r="W13" s="231"/>
+      <c r="W13" s="235"/>
       <c r="X13" s="121"/>
       <c r="Y13" s="121"/>
       <c r="Z13" s="120"/>
       <c r="AA13" s="120"/>
-      <c r="AD13" s="231" t="s">
+      <c r="AD13" s="235" t="s">
         <v>100</v>
       </c>
-      <c r="AE13" s="231"/>
+      <c r="AE13" s="235"/>
       <c r="AF13" s="121"/>
       <c r="AG13" s="121"/>
       <c r="AH13" s="120"/>
       <c r="AI13" s="120"/>
-      <c r="AL13" s="231" t="s">
+      <c r="AL13" s="235" t="s">
         <v>100</v>
       </c>
-      <c r="AM13" s="231"/>
+      <c r="AM13" s="235"/>
       <c r="AN13" s="121"/>
       <c r="AO13" s="121"/>
       <c r="AP13" s="120"/>
       <c r="AQ13" s="120"/>
-      <c r="AT13" s="231" t="s">
+      <c r="AT13" s="235" t="s">
         <v>100</v>
       </c>
-      <c r="AU13" s="231"/>
-    </row>
-    <row r="14" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="239"/>
+      <c r="AU13" s="235"/>
+    </row>
+    <row r="14" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="226"/>
       <c r="C14" s="156"/>
       <c r="D14" s="151">
         <v>5</v>
@@ -17186,14 +17493,14 @@
       <c r="AO14" s="120"/>
       <c r="AP14" s="119"/>
     </row>
-    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:51" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="157"/>
       <c r="C15" s="158" t="s">
         <v>125</v>
       </c>
       <c r="D15" s="159">
         <f>D14+D12+D10+D8+D6+D4</f>
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="E15" s="160"/>
       <c r="G15" s="119"/>
@@ -17213,27 +17520,27 @@
       <c r="AO15" s="120"/>
       <c r="AP15" s="119"/>
     </row>
-    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="31"/>
       <c r="C16" s="31"/>
-      <c r="D16" s="226">
+      <c r="D16" s="237">
         <f>SUM(D4:D14)</f>
-        <v>905</v>
+        <v>545</v>
       </c>
       <c r="E16" s="31"/>
     </row>
-    <row r="17" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:32" ht="14.1" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="31"/>
       <c r="C17" s="111" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="227"/>
+      <c r="D17" s="238"/>
       <c r="E17" s="31"/>
     </row>
-    <row r="18" spans="2:32" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C18" s="2"/>
     </row>
-    <row r="21" spans="2:32" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:32" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="N21" s="2"/>
       <c r="S21" s="2"/>
       <c r="T21" s="112"/>
@@ -17244,15 +17551,15 @@
       <c r="AB21" s="168" t="s">
         <v>96</v>
       </c>
-      <c r="AC21" s="237">
+      <c r="AC21" s="233">
         <f>D15</f>
-        <v>10</v>
-      </c>
-      <c r="AD21" s="237"/>
-      <c r="AE21" s="237"/>
-      <c r="AF21" s="237"/>
-    </row>
-    <row r="22" spans="2:32" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="AD21" s="233"/>
+      <c r="AE21" s="233"/>
+      <c r="AF21" s="233"/>
+    </row>
+    <row r="22" spans="2:32" x14ac:dyDescent="0.55000000000000004">
       <c r="N22" s="2"/>
       <c r="S22" s="2"/>
       <c r="T22" s="112"/>
@@ -17261,7 +17568,7 @@
       <c r="Z22" s="2"/>
       <c r="AA22" s="2"/>
     </row>
-    <row r="23" spans="2:32" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:32" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="N23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="112"/>
@@ -17272,15 +17579,15 @@
       <c r="AB23" s="168" t="s">
         <v>97</v>
       </c>
-      <c r="AC23" s="236">
+      <c r="AC23" s="232">
         <f>D16</f>
-        <v>905</v>
-      </c>
-      <c r="AD23" s="236"/>
-      <c r="AE23" s="236"/>
-      <c r="AF23" s="236"/>
-    </row>
-    <row r="24" spans="2:32" x14ac:dyDescent="0.25">
+        <v>545</v>
+      </c>
+      <c r="AD23" s="232"/>
+      <c r="AE23" s="232"/>
+      <c r="AF23" s="232"/>
+    </row>
+    <row r="24" spans="2:32" x14ac:dyDescent="0.55000000000000004">
       <c r="N24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="112"/>
@@ -17289,7 +17596,7 @@
       <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
     </row>
-    <row r="25" spans="2:32" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:32" ht="22.2" x14ac:dyDescent="0.55000000000000004">
       <c r="N25" s="2"/>
       <c r="S25" s="2"/>
       <c r="T25" s="112"/>
@@ -17300,22 +17607,32 @@
       <c r="AB25" s="168" t="s">
         <v>98</v>
       </c>
-      <c r="AC25" s="235">
+      <c r="AC25" s="231">
         <f>AC21/AC23</f>
-        <v>1.1049723756906077E-2</v>
-      </c>
-      <c r="AD25" s="235"/>
-      <c r="AE25" s="235"/>
-      <c r="AF25" s="235"/>
+        <v>0.11559633027522936</v>
+      </c>
+      <c r="AD25" s="231"/>
+      <c r="AE25" s="231"/>
+      <c r="AF25" s="231"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1"/>
   <mergeCells count="36">
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="AP4:AQ4"/>
-    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="AT12:AU12"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="G5:H6"/>
+    <mergeCell ref="Z11:AA11"/>
+    <mergeCell ref="AW5:AY5"/>
+    <mergeCell ref="AL13:AM13"/>
+    <mergeCell ref="AL12:AM12"/>
+    <mergeCell ref="AP3:AQ3"/>
+    <mergeCell ref="AD13:AE13"/>
+    <mergeCell ref="AH11:AI11"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="V12:W12"/>
+    <mergeCell ref="Z4:AA4"/>
     <mergeCell ref="AC25:AF25"/>
     <mergeCell ref="AC23:AF23"/>
     <mergeCell ref="AC21:AF21"/>
@@ -17332,21 +17649,11 @@
     <mergeCell ref="R3:S3"/>
     <mergeCell ref="Z3:AA3"/>
     <mergeCell ref="AH3:AI3"/>
-    <mergeCell ref="AP3:AQ3"/>
-    <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="AH11:AI11"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="V12:W12"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="AT12:AU12"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="G5:H6"/>
-    <mergeCell ref="Z11:AA11"/>
-    <mergeCell ref="AW5:AY5"/>
-    <mergeCell ref="AL13:AM13"/>
-    <mergeCell ref="AL12:AM12"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="AP4:AQ4"/>
+    <mergeCell ref="AD12:AE12"/>
   </mergeCells>
   <conditionalFormatting sqref="J5:J6 R5:R6 Z5:Z6 AH5:AH6 AP5:AP6">
     <cfRule type="expression" dxfId="9" priority="49">
@@ -17385,222 +17692,4 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="4.42578125" customWidth="1"/>
-    <col min="3" max="3" width="104.28515625" customWidth="1"/>
-    <col min="4" max="7" width="5.7109375" style="98" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="241" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="241"/>
-      <c r="C1" s="241"/>
-      <c r="D1" s="241"/>
-      <c r="E1" s="241"/>
-      <c r="F1" s="241"/>
-      <c r="G1" s="241"/>
-    </row>
-    <row r="2" spans="1:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="108" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="108" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="108" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="108" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="99"/>
-      <c r="C4" s="100" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="101" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="101" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="102" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="103">
-        <v>1</v>
-      </c>
-      <c r="C5" s="104" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="95"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="97"/>
-    </row>
-    <row r="6" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="103">
-        <v>2</v>
-      </c>
-      <c r="C6" s="104" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="95"/>
-      <c r="E6" s="96"/>
-      <c r="F6" s="96"/>
-      <c r="G6" s="97"/>
-    </row>
-    <row r="7" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="103">
-        <v>3</v>
-      </c>
-      <c r="C7" s="104" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="95"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="97"/>
-    </row>
-    <row r="8" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="103">
-        <v>4</v>
-      </c>
-      <c r="C8" s="104" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="95"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="97"/>
-    </row>
-    <row r="9" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="103">
-        <v>5</v>
-      </c>
-      <c r="C9" s="104" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="95"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="97"/>
-    </row>
-    <row r="10" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="103">
-        <v>6</v>
-      </c>
-      <c r="C10" s="104" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="95"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="97"/>
-    </row>
-    <row r="11" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="103">
-        <v>7</v>
-      </c>
-      <c r="C11" s="104" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="95"/>
-      <c r="E11" s="96"/>
-      <c r="F11" s="96"/>
-      <c r="G11" s="97"/>
-    </row>
-    <row r="12" spans="1:7" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="105">
-        <v>8</v>
-      </c>
-      <c r="C12" s="106" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="95"/>
-      <c r="E12" s="96"/>
-      <c r="F12" s="96"/>
-      <c r="G12" s="97"/>
-    </row>
-    <row r="13" spans="1:7" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D14" s="107">
-        <f>SUM(D5:D12)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="107">
-        <f>SUM(E5:E12)</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="107">
-        <f>SUM(F5:F12)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="107">
-        <f>SUM(G5:G12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="D16" s="109" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="240">
-        <f>SUM(D14:G14)/32</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="240"/>
-    </row>
-  </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="2">
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="D5:D12">
-    <cfRule type="cellIs" dxfId="3" priority="8" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E12">
-    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
-      <formula>2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F12">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
-      <formula>3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G12">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
-      <formula>4</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="A1:G1" location="Sommaire!A1" display="Enquête Motivation" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>